--- a/data/trans_orig/P33_2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33_2_2023-Provincia-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que duerme habitualmente al día durante los fines de semana</t>
+          <t>Número medio de horas que duerme habitualmente al día durante los fines de semana (tasa de respuesta: 97,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,09; 7,43</t>
+          <t>7,09; 7,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,09</t>
+          <t>6,88; 7,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 7,81</t>
+          <t>7,5; 7,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,73</t>
+          <t>7,54; 7,72</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,35</t>
+          <t>7,11; 7,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,35</t>
+          <t>7,19; 7,36</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,44</t>
+          <t>7,05; 7,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,26</t>
+          <t>7,07; 7,28</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 7,06</t>
+          <t>6,8; 7,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 6,82</t>
+          <t>6,65; 6,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 6,9</t>
+          <t>6,75; 6,91</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,33</t>
+          <t>7,04; 7,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,04</t>
+          <t>6,79; 7,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,36</t>
+          <t>7,12; 7,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,22</t>
+          <t>6,44; 7,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,67; 7,23</t>
+          <t>6,69; 7,23</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,67; 9,24</t>
+          <t>7,67; 9,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,49; 7,62</t>
+          <t>7,49; 7,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,61; 8,76</t>
+          <t>7,61; 8,73</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,08</t>
+          <t>7,36; 8,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,26</t>
+          <t>6,99; 7,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,67</t>
+          <t>7,24; 7,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33_2_2023-Provincia-trans_orig.xlsx
@@ -548,12 +548,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>7,22</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>7,05</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,09; 7,42</t>
+          <t>7,09; 7,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 7,1</t>
+          <t>6,94; 7,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,23</t>
+          <t>7,05; 7,23</t>
         </is>
       </c>
     </row>
@@ -598,12 +598,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,65</t>
+          <t>7,66</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,6</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -621,12 +621,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,82</t>
+          <t>7,51; 7,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 7,73</t>
+          <t>7,5; 7,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>7,27</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>7,22</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>7,24</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,45</t>
+          <t>7,14; 7,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,35</t>
+          <t>7,1; 7,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,36</t>
+          <t>7,15; 7,33</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>7,22</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,14</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,16</t>
+          <t>7,18</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,43</t>
+          <t>7,04; 7,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,22</t>
+          <t>7,0; 7,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,28</t>
+          <t>7,07; 7,29</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>6,95</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>6,83</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,05</t>
+          <t>6,84; 7,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 6,83</t>
+          <t>6,64; 6,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 6,91</t>
+          <t>6,76; 6,91</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>6,91</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,05</t>
+          <t>7,04</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,34</t>
+          <t>7,03; 7,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,04</t>
+          <t>6,79; 7,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,15</t>
+          <t>6,94; 7,14</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>7,27</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,04</t>
+          <t>7,22</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,38</t>
+          <t>7,14; 7,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 7,22</t>
+          <t>7,07; 7,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,69; 7,23</t>
+          <t>7,14; 7,3</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>7,71</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7,97</t>
+          <t>7,63</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,67; 9,23</t>
+          <t>7,64; 7,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,49; 7,61</t>
+          <t>7,49; 7,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,61; 8,73</t>
+          <t>7,58; 7,68</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,38</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,32</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,36; 8,13</t>
+          <t>7,34; 7,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,26</t>
+          <t>7,22; 7,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,72</t>
+          <t>7,29; 7,35</t>
         </is>
       </c>
     </row>
